--- a/Unity/Assets/Editor/ExcelTool/Excel/Language.xlsx
+++ b/Unity/Assets/Editor/ExcelTool/Excel/Language.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>Id</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Japanese</t>
   </si>
   <si>
-    <t>mark</t>
+    <t>UI_Login.username</t>
   </si>
   <si>
     <t>Username</t>
@@ -37,7 +37,7 @@
     <t>输入用户名</t>
   </si>
   <si>
-    <t>ui_login.username</t>
+    <t>UI_Login.password</t>
   </si>
   <si>
     <t>Password</t>
@@ -46,7 +46,7 @@
     <t>输入密码</t>
   </si>
   <si>
-    <t>ui_login.password</t>
+    <t>UI_Login.login</t>
   </si>
   <si>
     <t>LOGIN</t>
@@ -55,16 +55,16 @@
     <t>登录</t>
   </si>
   <si>
-    <t>ui_login.login</t>
-  </si>
-  <si>
-    <t>Don't have an account? Sign Up</t>
+    <t>UI_Login.toregister</t>
+  </si>
+  <si>
+    <t>Go Register</t>
   </si>
   <si>
     <t>去注册</t>
   </si>
   <si>
-    <t>ui_login.toregister</t>
+    <t>UI_Login.password2</t>
   </si>
   <si>
     <t>Repeat Password</t>
@@ -73,7 +73,7 @@
     <t>确认密码</t>
   </si>
   <si>
-    <t>ui_login.password2</t>
+    <t>UI_Login.register</t>
   </si>
   <si>
     <t>CREATE ACCOUNT</t>
@@ -82,16 +82,82 @@
     <t>注册</t>
   </si>
   <si>
-    <t>ui_login.register</t>
-  </si>
-  <si>
-    <t>Already have an account? Login here</t>
+    <t>UI_Login.tologin</t>
+  </si>
+  <si>
+    <t>Login here</t>
   </si>
   <si>
     <t>去登录</t>
   </si>
   <si>
-    <t>ui_login.tologin</t>
+    <t>UI_Lobby.Arcade</t>
+  </si>
+  <si>
+    <t>Arcade</t>
+  </si>
+  <si>
+    <t>剧情</t>
+  </si>
+  <si>
+    <t>UI_Lobby.Match</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>匹配</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>训练</t>
+  </si>
+  <si>
+    <t>Replay</t>
+  </si>
+  <si>
+    <t>回放</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>Exit</t>
+  </si>
+  <si>
+    <t>退出</t>
+  </si>
+  <si>
+    <t>UI_Matching.UsedTime</t>
+  </si>
+  <si>
+    <t>Used Time:</t>
+  </si>
+  <si>
+    <t>已用时间：</t>
+  </si>
+  <si>
+    <t>UI_Matching.Cancel</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>取消</t>
+  </si>
+  <si>
+    <t>UI_RoleSelect.Back</t>
+  </si>
+  <si>
+    <t>BACK</t>
+  </si>
+  <si>
+    <t>返回</t>
   </si>
 </sst>
 </file>
@@ -1029,16 +1095,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="4.66666666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6666666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.75" customWidth="1"/>
     <col min="3" max="3" width="10.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="17.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="7.33333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1051,13 +1117,10 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1">
-        <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -1065,13 +1128,10 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1">
-        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -1079,13 +1139,10 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1">
-        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -1093,13 +1150,10 @@
       <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1">
-        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -1107,13 +1161,10 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1">
-        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -1121,13 +1172,10 @@
       <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1">
-        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -1135,13 +1183,10 @@
       <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1">
-        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -1149,8 +1194,104 @@
       <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="E8" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
